--- a/data/availability/projects/palm-hills-developments/px.xlsx
+++ b/data/availability/projects/palm-hills-developments/px.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for px</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -909,7 +919,6 @@
       <c r="G2" t="n">
         <v>213.61</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -966,7 +975,6 @@
       <c r="G3" t="n">
         <v>200.72</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1023,7 +1031,6 @@
       <c r="G4" t="n">
         <v>200.72</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1080,7 +1087,6 @@
       <c r="G5" t="n">
         <v>200.72</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1137,7 +1143,6 @@
       <c r="G6" t="n">
         <v>200.72</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1194,7 +1199,6 @@
       <c r="G7" t="n">
         <v>200.72</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1251,7 +1255,6 @@
       <c r="G8" t="n">
         <v>200.72</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1308,7 +1311,6 @@
       <c r="G9" t="n">
         <v>200.72</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1365,7 +1367,6 @@
       <c r="G10" t="n">
         <v>200.72</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1422,7 +1423,6 @@
       <c r="G11" t="n">
         <v>200.72</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1479,7 +1479,6 @@
       <c r="G12" t="n">
         <v>200.72</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1536,7 +1535,6 @@
       <c r="G13" t="n">
         <v>200.72</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1593,7 +1591,6 @@
       <c r="G14" t="n">
         <v>200.72</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1650,7 +1647,6 @@
       <c r="G15" t="n">
         <v>200.72</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1707,7 +1703,6 @@
       <c r="G16" t="n">
         <v>200.72</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1764,7 +1759,6 @@
       <c r="G17" t="n">
         <v>152.9</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1821,7 +1815,6 @@
       <c r="G18" t="n">
         <v>160.92</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1878,7 +1871,6 @@
       <c r="G19" t="n">
         <v>139.65</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1935,7 +1927,6 @@
       <c r="G20" t="n">
         <v>138.48</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1992,7 +1983,6 @@
       <c r="G21" t="n">
         <v>152.9</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2049,7 +2039,6 @@
       <c r="G22" t="n">
         <v>138.19</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2106,7 +2095,6 @@
       <c r="G23" t="n">
         <v>138.19</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2163,7 +2151,6 @@
       <c r="G24" t="n">
         <v>152.9</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2220,7 +2207,6 @@
       <c r="G25" t="n">
         <v>152.9</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2277,7 +2263,6 @@
       <c r="G26" t="n">
         <v>138.48</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2334,7 +2319,6 @@
       <c r="G27" t="n">
         <v>139.65</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2391,7 +2375,6 @@
       <c r="G28" t="n">
         <v>152.9</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2448,7 +2431,6 @@
       <c r="G29" t="n">
         <v>139.65</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2505,7 +2487,6 @@
       <c r="G30" t="n">
         <v>138.48</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2562,7 +2543,6 @@
       <c r="G31" t="n">
         <v>160.92</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2619,7 +2599,6 @@
       <c r="G32" t="n">
         <v>139.65</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2676,7 +2655,6 @@
       <c r="G33" t="n">
         <v>171.17</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2733,7 +2711,6 @@
       <c r="G34" t="n">
         <v>152.9</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2790,7 +2767,6 @@
       <c r="G35" t="n">
         <v>139.65</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2847,7 +2823,6 @@
       <c r="G36" t="n">
         <v>77.84</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2904,7 +2879,6 @@
       <c r="G37" t="n">
         <v>171.17</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2961,7 +2935,6 @@
       <c r="G38" t="n">
         <v>138.48</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3018,7 +2991,6 @@
       <c r="G39" t="n">
         <v>152.9</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3075,7 +3047,6 @@
       <c r="G40" t="n">
         <v>160.92</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3132,7 +3103,6 @@
       <c r="G41" t="n">
         <v>139.65</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3189,7 +3159,6 @@
       <c r="G42" t="n">
         <v>171.17</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3246,7 +3215,6 @@
       <c r="G43" t="n">
         <v>139.65</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3303,7 +3271,6 @@
       <c r="G44" t="n">
         <v>138.48</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3360,7 +3327,6 @@
       <c r="G45" t="n">
         <v>152.9</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3417,7 +3383,6 @@
       <c r="G46" t="n">
         <v>139.65</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3474,7 +3439,6 @@
       <c r="G47" t="n">
         <v>77.84</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3531,7 +3495,6 @@
       <c r="G48" t="n">
         <v>171.17</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3588,7 +3551,6 @@
       <c r="G49" t="n">
         <v>138.48</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3645,7 +3607,6 @@
       <c r="G50" t="n">
         <v>77.84</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3702,7 +3663,6 @@
       <c r="G51" t="n">
         <v>139.65</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3759,7 +3719,6 @@
       <c r="G52" t="n">
         <v>77.84</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3816,7 +3775,6 @@
       <c r="G53" t="n">
         <v>171.17</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3873,7 +3831,6 @@
       <c r="G54" t="n">
         <v>138.48</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3930,7 +3887,6 @@
       <c r="G55" t="n">
         <v>77.84</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3987,7 +3943,6 @@
       <c r="G56" t="n">
         <v>160.92</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4044,7 +3999,6 @@
       <c r="G57" t="n">
         <v>139.65</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4101,7 +4055,6 @@
       <c r="G58" t="n">
         <v>77.84</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4158,7 +4111,6 @@
       <c r="G59" t="n">
         <v>171.17</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4215,7 +4167,6 @@
       <c r="G60" t="n">
         <v>138.48</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4272,7 +4223,6 @@
       <c r="G61" t="n">
         <v>77.84</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4329,7 +4279,6 @@
       <c r="G62" t="n">
         <v>160.92</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4386,7 +4335,6 @@
       <c r="G63" t="n">
         <v>139.65</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4443,7 +4391,6 @@
       <c r="G64" t="n">
         <v>77.84</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4500,7 +4447,6 @@
       <c r="G65" t="n">
         <v>171.17</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4557,7 +4503,6 @@
       <c r="G66" t="n">
         <v>138.48</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4614,7 +4559,6 @@
       <c r="G67" t="n">
         <v>77.84</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4671,7 +4615,6 @@
       <c r="G68" t="n">
         <v>152.9</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4728,7 +4671,6 @@
       <c r="G69" t="n">
         <v>160.92</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4785,7 +4727,6 @@
       <c r="G70" t="n">
         <v>152.9</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4842,7 +4783,6 @@
       <c r="G71" t="n">
         <v>160.92</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4899,7 +4839,6 @@
       <c r="G72" t="n">
         <v>139.65</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4956,7 +4895,6 @@
       <c r="G73" t="n">
         <v>138.48</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5013,7 +4951,6 @@
       <c r="G74" t="n">
         <v>152.9</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5070,7 +5007,6 @@
       <c r="G75" t="n">
         <v>160.92</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5127,7 +5063,6 @@
       <c r="G76" t="n">
         <v>139.65</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5184,7 +5119,6 @@
       <c r="G77" t="n">
         <v>138.48</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5241,7 +5175,6 @@
       <c r="G78" t="n">
         <v>77.84</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5298,7 +5231,6 @@
       <c r="G79" t="n">
         <v>152.9</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5355,7 +5287,6 @@
       <c r="G80" t="n">
         <v>139.65</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5412,7 +5343,6 @@
       <c r="G81" t="n">
         <v>77.84</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5469,7 +5399,6 @@
       <c r="G82" t="n">
         <v>138.48</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5526,7 +5455,6 @@
       <c r="G83" t="n">
         <v>77.84</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5583,7 +5511,6 @@
       <c r="G84" t="n">
         <v>160.92</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5640,7 +5567,6 @@
       <c r="G85" t="n">
         <v>139.65</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5697,7 +5623,6 @@
       <c r="G86" t="n">
         <v>77.84</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5754,7 +5679,6 @@
       <c r="G87" t="n">
         <v>138.48</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5811,7 +5735,6 @@
       <c r="G88" t="n">
         <v>152.9</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5868,7 +5791,6 @@
       <c r="G89" t="n">
         <v>160.92</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5925,7 +5847,6 @@
       <c r="G90" t="n">
         <v>160.92</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5982,7 +5903,6 @@
       <c r="G91" t="n">
         <v>77.84</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6039,7 +5959,6 @@
       <c r="G92" t="n">
         <v>160.92</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6096,7 +6015,6 @@
       <c r="G93" t="n">
         <v>139.65</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6153,7 +6071,6 @@
       <c r="G94" t="n">
         <v>77.84</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6210,7 +6127,6 @@
       <c r="G95" t="n">
         <v>152.9</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6267,7 +6183,6 @@
       <c r="G96" t="n">
         <v>160.92</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6324,7 +6239,6 @@
       <c r="G97" t="n">
         <v>139.65</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6381,7 +6295,6 @@
       <c r="G98" t="n">
         <v>77.84</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6438,7 +6351,6 @@
       <c r="G99" t="n">
         <v>152.9</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6495,7 +6407,6 @@
       <c r="G100" t="n">
         <v>160.92</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6552,7 +6463,6 @@
       <c r="G101" t="n">
         <v>139.65</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6609,7 +6519,6 @@
       <c r="G102" t="n">
         <v>171.17</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6666,7 +6575,6 @@
       <c r="G103" t="n">
         <v>138.48</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6723,7 +6631,6 @@
       <c r="G104" t="n">
         <v>139.65</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6780,7 +6687,6 @@
       <c r="G105" t="n">
         <v>171.17</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6837,7 +6743,6 @@
       <c r="G106" t="n">
         <v>138.48</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6894,7 +6799,6 @@
       <c r="G107" t="n">
         <v>152.9</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6951,7 +6855,6 @@
       <c r="G108" t="n">
         <v>139.65</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7008,7 +6911,6 @@
       <c r="G109" t="n">
         <v>171.17</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7065,7 +6967,6 @@
       <c r="G110" t="n">
         <v>138.48</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7122,7 +7023,6 @@
       <c r="G111" t="n">
         <v>77.84</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7179,7 +7079,6 @@
       <c r="G112" t="n">
         <v>170.17</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7236,7 +7135,6 @@
       <c r="G113" t="n">
         <v>152.9</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7293,7 +7191,6 @@
       <c r="G114" t="n">
         <v>139.65</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7350,7 +7247,6 @@
       <c r="G115" t="n">
         <v>171.17</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7407,7 +7303,6 @@
       <c r="G116" t="n">
         <v>138.48</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7464,7 +7359,6 @@
       <c r="G117" t="n">
         <v>170.17</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7521,7 +7415,6 @@
       <c r="G118" t="n">
         <v>152.9</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7578,7 +7471,6 @@
       <c r="G119" t="n">
         <v>139.65</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7635,7 +7527,6 @@
       <c r="G120" t="n">
         <v>171.17</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7692,7 +7583,6 @@
       <c r="G121" t="n">
         <v>138.48</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7749,7 +7639,6 @@
       <c r="G122" t="n">
         <v>170.17</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7806,7 +7695,6 @@
       <c r="G123" t="n">
         <v>139.65</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7863,7 +7751,6 @@
       <c r="G124" t="n">
         <v>138.48</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7920,7 +7807,6 @@
       <c r="G125" t="n">
         <v>77.84</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7977,7 +7863,6 @@
       <c r="G126" t="n">
         <v>164.48</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8034,7 +7919,6 @@
       <c r="G127" t="n">
         <v>164.48</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8091,7 +7975,6 @@
       <c r="G128" t="n">
         <v>139.65</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8148,7 +8031,6 @@
       <c r="G129" t="n">
         <v>139.65</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8205,7 +8087,6 @@
       <c r="G130" t="n">
         <v>139.65</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8262,7 +8143,6 @@
       <c r="G131" t="n">
         <v>138.48</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8319,7 +8199,6 @@
       <c r="G132" t="n">
         <v>139.65</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8376,7 +8255,6 @@
       <c r="G133" t="n">
         <v>138.48</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8433,7 +8311,6 @@
       <c r="G134" t="n">
         <v>129.86</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8490,7 +8367,6 @@
       <c r="G135" t="n">
         <v>138.19</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8547,7 +8423,6 @@
       <c r="G136" t="n">
         <v>152.9</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8604,7 +8479,6 @@
       <c r="G137" t="n">
         <v>139.65</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8661,7 +8535,6 @@
       <c r="G138" t="n">
         <v>138.48</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8718,7 +8591,6 @@
       <c r="G139" t="n">
         <v>77.84</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8775,7 +8647,6 @@
       <c r="G140" t="n">
         <v>77.84</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8832,7 +8703,6 @@
       <c r="G141" t="n">
         <v>129.86</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8889,7 +8759,6 @@
       <c r="G142" t="n">
         <v>130.88</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8946,7 +8815,6 @@
       <c r="G143" t="n">
         <v>171.8</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9003,7 +8871,6 @@
       <c r="G144" t="n">
         <v>138.19</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9060,7 +8927,6 @@
       <c r="G145" t="n">
         <v>119.16</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9117,7 +8983,6 @@
       <c r="G146" t="n">
         <v>144.18</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9174,7 +9039,6 @@
       <c r="G147" t="n">
         <v>156.56</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9231,7 +9095,6 @@
       <c r="G148" t="n">
         <v>164.48</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9288,7 +9151,6 @@
       <c r="G149" t="n">
         <v>156.56</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9345,7 +9207,6 @@
       <c r="G150" t="n">
         <v>164.48</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9402,7 +9263,6 @@
       <c r="G151" t="n">
         <v>156.56</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9459,7 +9319,6 @@
       <c r="G152" t="n">
         <v>164.48</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9516,7 +9375,6 @@
       <c r="G153" t="n">
         <v>156.56</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9573,7 +9431,6 @@
       <c r="G154" t="n">
         <v>129.86</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9630,7 +9487,6 @@
       <c r="G155" t="n">
         <v>138.19</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9687,7 +9543,6 @@
       <c r="G156" t="n">
         <v>138.19</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9744,7 +9599,6 @@
       <c r="G157" t="n">
         <v>129.86</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9801,7 +9655,6 @@
       <c r="G158" t="n">
         <v>138.19</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9858,7 +9711,6 @@
       <c r="G159" t="n">
         <v>138.19</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9915,7 +9767,6 @@
       <c r="G160" t="n">
         <v>164.48</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9972,7 +9823,6 @@
       <c r="G161" t="n">
         <v>156.56</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10029,7 +9879,6 @@
       <c r="G162" t="n">
         <v>164.48</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10086,7 +9935,6 @@
       <c r="G163" t="n">
         <v>156.56</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10143,7 +9991,6 @@
       <c r="G164" t="n">
         <v>164.48</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10200,7 +10047,6 @@
       <c r="G165" t="n">
         <v>164.48</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10257,7 +10103,6 @@
       <c r="G166" t="n">
         <v>129.86</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10314,7 +10159,6 @@
       <c r="G167" t="n">
         <v>130.88</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10371,7 +10215,6 @@
       <c r="G168" t="n">
         <v>119.16</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10428,7 +10271,6 @@
       <c r="G169" t="n">
         <v>129.86</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10485,7 +10327,6 @@
       <c r="G170" t="n">
         <v>130.88</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10542,7 +10383,6 @@
       <c r="G171" t="n">
         <v>138.19</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10599,7 +10439,6 @@
       <c r="G172" t="n">
         <v>129.86</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10656,7 +10495,6 @@
       <c r="G173" t="n">
         <v>130.88</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10713,7 +10551,6 @@
       <c r="G174" t="n">
         <v>138.19</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10770,7 +10607,6 @@
       <c r="G175" t="n">
         <v>129.86</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10827,7 +10663,6 @@
       <c r="G176" t="n">
         <v>129.86</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10884,7 +10719,6 @@
       <c r="G177" t="n">
         <v>77.84</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10941,7 +10775,6 @@
       <c r="G178" t="n">
         <v>77.84</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10998,7 +10831,6 @@
       <c r="G179" t="n">
         <v>129.86</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11055,7 +10887,6 @@
       <c r="G180" t="n">
         <v>138.19</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11112,7 +10943,6 @@
       <c r="G181" t="n">
         <v>138.19</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11169,7 +10999,6 @@
       <c r="G182" t="n">
         <v>130.88</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11226,7 +11055,6 @@
       <c r="G183" t="n">
         <v>164.48</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11283,7 +11111,6 @@
       <c r="G184" t="n">
         <v>164.48</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11340,7 +11167,6 @@
       <c r="G185" t="n">
         <v>139.65</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11397,7 +11223,6 @@
       <c r="G186" t="n">
         <v>171.17</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11454,7 +11279,6 @@
       <c r="G187" t="n">
         <v>170.17</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11511,7 +11335,6 @@
       <c r="G188" t="n">
         <v>130.88</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11568,7 +11391,6 @@
       <c r="G189" t="n">
         <v>138.19</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11625,7 +11447,6 @@
       <c r="G190" t="n">
         <v>130.88</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11682,7 +11503,6 @@
       <c r="G191" t="n">
         <v>138.19</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11739,7 +11559,6 @@
       <c r="G192" t="n">
         <v>129.86</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11796,7 +11615,6 @@
       <c r="G193" t="n">
         <v>129.86</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11853,7 +11671,6 @@
       <c r="G194" t="n">
         <v>130.88</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11910,7 +11727,6 @@
       <c r="G195" t="n">
         <v>129.86</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11967,7 +11783,6 @@
       <c r="G196" t="n">
         <v>130.88</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12024,7 +11839,6 @@
       <c r="G197" t="n">
         <v>130.88</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12081,7 +11895,6 @@
       <c r="G198" t="n">
         <v>130.88</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12138,7 +11951,6 @@
       <c r="G199" t="n">
         <v>129.86</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12195,7 +12007,6 @@
       <c r="G200" t="n">
         <v>139.65</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12252,7 +12063,6 @@
       <c r="G201" t="n">
         <v>138.48</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12309,7 +12119,6 @@
       <c r="G202" t="n">
         <v>139.65</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12366,7 +12175,6 @@
       <c r="G203" t="n">
         <v>138.48</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12423,7 +12231,6 @@
       <c r="G204" t="n">
         <v>130.88</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12480,7 +12287,6 @@
       <c r="G205" t="n">
         <v>138.19</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12537,7 +12343,6 @@
       <c r="G206" t="n">
         <v>139.65</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12594,7 +12399,6 @@
       <c r="G207" t="n">
         <v>138.48</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12651,7 +12455,6 @@
       <c r="G208" t="n">
         <v>138.48</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12708,7 +12511,6 @@
       <c r="G209" t="n">
         <v>129.86</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12765,7 +12567,6 @@
       <c r="G210" t="n">
         <v>129.86</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12822,7 +12623,6 @@
       <c r="G211" t="n">
         <v>130.88</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12879,7 +12679,6 @@
       <c r="G212" t="n">
         <v>138.19</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12936,7 +12735,6 @@
       <c r="G213" t="n">
         <v>139.65</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12993,7 +12791,6 @@
       <c r="G214" t="n">
         <v>170.17</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13050,7 +12847,6 @@
       <c r="G215" t="n">
         <v>171.17</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13107,7 +12903,6 @@
       <c r="G216" t="n">
         <v>200.72</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13164,7 +12959,6 @@
       <c r="G217" t="n">
         <v>200.72</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13221,7 +13015,6 @@
       <c r="G218" t="n">
         <v>213.61</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13278,7 +13071,6 @@
       <c r="G219" t="n">
         <v>208.02</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13335,7 +13127,6 @@
       <c r="G220" t="n">
         <v>200.72</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13392,7 +13183,6 @@
       <c r="G221" t="n">
         <v>213.61</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13449,7 +13239,6 @@
       <c r="G222" t="n">
         <v>200.72</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13506,7 +13295,6 @@
       <c r="G223" t="n">
         <v>200.72</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13563,7 +13351,6 @@
       <c r="G224" t="n">
         <v>200.72</v>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13620,7 +13407,6 @@
       <c r="G225" t="n">
         <v>200.72</v>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13677,7 +13463,6 @@
       <c r="G226" t="n">
         <v>200.72</v>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13734,7 +13519,6 @@
       <c r="G227" t="n">
         <v>213.61</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13791,7 +13575,6 @@
       <c r="G228" t="n">
         <v>208.02</v>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13848,7 +13631,6 @@
       <c r="G229" t="n">
         <v>200.72</v>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13905,7 +13687,6 @@
       <c r="G230" t="n">
         <v>200.72</v>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13962,7 +13743,6 @@
       <c r="G231" t="n">
         <v>200.72</v>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14019,7 +13799,6 @@
       <c r="G232" t="n">
         <v>200.72</v>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14076,7 +13855,6 @@
       <c r="G233" t="n">
         <v>200.72</v>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14133,7 +13911,6 @@
       <c r="G234" t="n">
         <v>208.02</v>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14190,7 +13967,6 @@
       <c r="G235" t="n">
         <v>200.72</v>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14247,7 +14023,6 @@
       <c r="G236" t="n">
         <v>200.72</v>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14304,7 +14079,6 @@
       <c r="G237" t="n">
         <v>200.72</v>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14361,7 +14135,6 @@
       <c r="G238" t="n">
         <v>200.72</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14418,7 +14191,6 @@
       <c r="G239" t="n">
         <v>200.72</v>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14475,7 +14247,6 @@
       <c r="G240" t="n">
         <v>200.72</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14532,7 +14303,6 @@
       <c r="G241" t="n">
         <v>313.67</v>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14589,7 +14359,6 @@
       <c r="G242" t="n">
         <v>200.72</v>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14646,7 +14415,6 @@
       <c r="G243" t="n">
         <v>200.72</v>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14703,7 +14471,6 @@
       <c r="G244" t="n">
         <v>200.72</v>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14760,7 +14527,6 @@
       <c r="G245" t="n">
         <v>200.72</v>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14817,7 +14583,6 @@
       <c r="G246" t="n">
         <v>208.02</v>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14874,7 +14639,6 @@
       <c r="G247" t="n">
         <v>200.72</v>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14931,7 +14695,6 @@
       <c r="G248" t="n">
         <v>200.72</v>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14988,7 +14751,6 @@
       <c r="G249" t="n">
         <v>200.72</v>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15045,7 +14807,6 @@
       <c r="G250" t="n">
         <v>200.72</v>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15102,7 +14863,6 @@
       <c r="G251" t="n">
         <v>213.61</v>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15159,7 +14919,6 @@
       <c r="G252" t="n">
         <v>200.72</v>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15216,7 +14975,6 @@
       <c r="G253" t="n">
         <v>200.72</v>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15273,7 +15031,6 @@
       <c r="G254" t="n">
         <v>200.72</v>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15330,7 +15087,6 @@
       <c r="G255" t="n">
         <v>200.72</v>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15387,7 +15143,6 @@
       <c r="G256" t="n">
         <v>200.72</v>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15444,7 +15199,6 @@
       <c r="G257" t="n">
         <v>200.72</v>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15501,7 +15255,6 @@
       <c r="G258" t="n">
         <v>200.72</v>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15558,7 +15311,6 @@
       <c r="G259" t="n">
         <v>200.72</v>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15615,7 +15367,6 @@
       <c r="G260" t="n">
         <v>200.72</v>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15672,7 +15423,6 @@
       <c r="G261" t="n">
         <v>200.72</v>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15729,7 +15479,6 @@
       <c r="G262" t="n">
         <v>200.72</v>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15786,7 +15535,6 @@
       <c r="G263" t="n">
         <v>200.72</v>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15843,7 +15591,6 @@
       <c r="G264" t="n">
         <v>200.72</v>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15900,7 +15647,6 @@
       <c r="G265" t="n">
         <v>200.72</v>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15957,7 +15703,6 @@
       <c r="G266" t="n">
         <v>200.72</v>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16014,7 +15759,6 @@
       <c r="G267" t="n">
         <v>200.72</v>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16071,7 +15815,6 @@
       <c r="G268" t="n">
         <v>200.72</v>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16128,7 +15871,6 @@
       <c r="G269" t="n">
         <v>200.72</v>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16185,7 +15927,6 @@
       <c r="G270" t="n">
         <v>200.72</v>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16242,7 +15983,6 @@
       <c r="G271" t="n">
         <v>200.72</v>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/px.xlsx
+++ b/data/availability/projects/palm-hills-developments/px.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
